--- a/data/trans_bre/P0902-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P0902-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 10,36</t>
+          <t>-0,28; 10,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,28; 20,66</t>
+          <t>7,48; 20,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,8; 21,09</t>
+          <t>7,83; 20,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 7,45</t>
+          <t>-0,63; 7,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 160,34</t>
+          <t>-3,94; 173,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,82; 191,82</t>
+          <t>46,65; 198,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,58; 266,34</t>
+          <t>58,73; 264,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 134,32</t>
+          <t>-9,24; 138,86</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 11,43</t>
+          <t>2,9; 11,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 12,1</t>
+          <t>2,78; 12,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 11,01</t>
+          <t>2,64; 10,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 11,8</t>
+          <t>2,34; 12,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,33; 152,7</t>
+          <t>22,59; 157,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,26; 142,37</t>
+          <t>20,72; 148,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,03; 159,65</t>
+          <t>24,48; 156,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,11; 82,01</t>
+          <t>11,67; 84,21</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 11,3</t>
+          <t>3,25; 11,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 11,26</t>
+          <t>0,22; 11,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 8,22</t>
+          <t>-0,88; 8,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 8,9</t>
+          <t>-0,72; 8,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,06; 344,19</t>
+          <t>42,99; 365,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 124,84</t>
+          <t>-0,17; 128,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 146,81</t>
+          <t>-10,56; 147,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 81,72</t>
+          <t>-4,85; 78,95</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 15,04</t>
+          <t>6,38; 14,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,03; 23,23</t>
+          <t>10,97; 22,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 20,11</t>
+          <t>7,15; 20,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 9,61</t>
+          <t>-7,63; 9,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>101,51; 586,73</t>
+          <t>113,35; 638,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,63; 188,26</t>
+          <t>60,74; 182,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,72; 147,08</t>
+          <t>36,32; 150,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,12; 61,85</t>
+          <t>-35,38; 61,31</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 9,96</t>
+          <t>-1,37; 10,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,11; 22,3</t>
+          <t>7,92; 22,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 11,84</t>
+          <t>0,24; 12,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 9,2</t>
+          <t>0,95; 9,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 190,66</t>
+          <t>-18,27; 201,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,62; 269,5</t>
+          <t>54,74; 285,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 209,9</t>
+          <t>-1,08; 239,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 207,84</t>
+          <t>9,17; 199,34</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 13,93</t>
+          <t>2,96; 13,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 9,64</t>
+          <t>-1,75; 10,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 13,65</t>
+          <t>0,61; 13,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,24; 8,68</t>
+          <t>0,02; 9,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,42; 225,6</t>
+          <t>26,09; 224,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 98,54</t>
+          <t>-12,09; 101,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 120,07</t>
+          <t>2,28; 125,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 99,97</t>
+          <t>0,65; 103,42</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 7,43</t>
+          <t>0,42; 7,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,73; 11,5</t>
+          <t>4,61; 11,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,38; 14,58</t>
+          <t>6,51; 14,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 10,23</t>
+          <t>-7,08; 10,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,83; 104,33</t>
+          <t>3,45; 98,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,1; 190,38</t>
+          <t>51,58; 205,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,66; 208,94</t>
+          <t>63,36; 205,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-34,53; 87,54</t>
+          <t>-46,66; 86,01</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,42</t>
+          <t>2,74; 9,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,92; 10,19</t>
+          <t>3,05; 10,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,84; 10,51</t>
+          <t>3,86; 9,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,4; 18,12</t>
+          <t>7,84; 17,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,85; 109,47</t>
+          <t>21,83; 114,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,96; 111,9</t>
+          <t>24,26; 118,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,13; 216,49</t>
+          <t>50,97; 207,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>60,64; 431,75</t>
+          <t>64,87; 378,62</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,88</t>
+          <t>4,93; 8,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,25; 10,76</t>
+          <t>7,06; 10,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,18</t>
+          <t>6,81; 10,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,04</t>
+          <t>3,09; 9,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>55,09; 104,62</t>
+          <t>56,61; 108,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62,05; 107,88</t>
+          <t>59,77; 104,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68,18; 119,32</t>
+          <t>66,81; 116,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>26,66; 91,91</t>
+          <t>26,11; 93,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P0902-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P0902-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>4,37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>59,38%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 10,67</t>
+          <t>-0,87; 9,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,48; 20,75</t>
+          <t>7,81; 21,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,83; 20,83</t>
+          <t>7,24; 20,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 7,7</t>
+          <t>0,48; 8,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 173,38</t>
+          <t>-8,17; 149,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,65; 198,36</t>
+          <t>47,2; 204,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,73; 264,67</t>
+          <t>51,2; 260,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 138,86</t>
+          <t>2,28; 156,55</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>6,29</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 11,46</t>
+          <t>2,99; 10,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 12,44</t>
+          <t>2,61; 12,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 10,77</t>
+          <t>2,73; 11,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 12,14</t>
+          <t>1,66; 10,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,59; 157,48</t>
+          <t>26,11; 149,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,72; 148,78</t>
+          <t>18,34; 148,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,48; 156,9</t>
+          <t>25,36; 172,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,67; 84,21</t>
+          <t>7,77; 72,68</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,3</t>
+          <t>4,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 11,74</t>
+          <t>2,89; 11,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 11,33</t>
+          <t>-0,42; 11,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 8,4</t>
+          <t>-0,98; 8,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 8,77</t>
+          <t>-0,37; 8,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,99; 365,55</t>
+          <t>45,37; 394,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 128,4</t>
+          <t>-4,93; 122,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 147,72</t>
+          <t>-11,16; 152,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 78,95</t>
+          <t>-2,99; 82,62</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>47,27%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,38; 14,75</t>
+          <t>6,87; 15,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,97; 22,66</t>
+          <t>10,83; 22,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 20,41</t>
+          <t>7,09; 20,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 9,36</t>
+          <t>2,02; 14,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>113,35; 638,97</t>
+          <t>118,78; 634,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,74; 182,77</t>
+          <t>58,96; 175,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,32; 150,13</t>
+          <t>36,94; 138,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 61,31</t>
+          <t>9,64; 104,96</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 10,28</t>
+          <t>-1,85; 9,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,92; 22,81</t>
+          <t>7,87; 22,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 12,45</t>
+          <t>-0,03; 11,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,06</t>
+          <t>1,11; 9,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 201,02</t>
+          <t>-22,48; 193,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,74; 285,63</t>
+          <t>48,0; 266,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 239,76</t>
+          <t>-2,69; 218,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,17; 199,34</t>
+          <t>9,92; 208,64</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>4,51</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,96; 13,56</t>
+          <t>3,31; 13,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 10,15</t>
+          <t>-2,17; 9,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 13,74</t>
+          <t>0,67; 13,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,02; 9,11</t>
+          <t>0,2; 9,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,09; 224,55</t>
+          <t>30,23; 231,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 101,99</t>
+          <t>-14,56; 99,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 125,55</t>
+          <t>3,53; 127,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 103,42</t>
+          <t>0,21; 102,9</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,87</t>
+          <t>10,02</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,57</t>
+          <t>0,35; 7,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,61; 11,6</t>
+          <t>4,32; 11,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,51; 14,27</t>
+          <t>6,41; 14,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 10,11</t>
+          <t>6,46; 13,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 98,81</t>
+          <t>3,41; 100,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,58; 205,64</t>
+          <t>52,14; 201,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,36; 205,56</t>
+          <t>62,1; 212,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 86,01</t>
+          <t>46,68; 132,35</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11,67</t>
+          <t>8,29</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>137,39%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,74; 9,7</t>
+          <t>2,69; 9,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,05; 10,33</t>
+          <t>3,27; 10,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,86; 9,69</t>
+          <t>3,75; 10,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,84; 17,48</t>
+          <t>4,92; 11,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,83; 114,36</t>
+          <t>21,92; 111,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,26; 118,8</t>
+          <t>26,16; 120,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,97; 207,92</t>
+          <t>51,62; 212,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>64,87; 378,62</t>
+          <t>37,09; 116,78</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,28</t>
+          <t>7,2</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,03</t>
+          <t>4,94; 8,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,06; 10,66</t>
+          <t>7,22; 10,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,06</t>
+          <t>6,71; 10,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,09; 9,1</t>
+          <t>5,68; 8,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>56,61; 108,33</t>
+          <t>55,91; 108,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59,77; 104,4</t>
+          <t>61,6; 105,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>66,81; 116,04</t>
+          <t>67,2; 119,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>26,11; 93,42</t>
+          <t>42,25; 73,94</t>
         </is>
       </c>
     </row>
